--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2763,7 +2763,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FOI email obfuscated by Cloudflare on FOI page; not confirmed; FOI email decoded from Cloudflare cfemail attribute on FOI page.</t>
+          <t>FOI email obfuscated by Cloudflare on FOI page; not confirmed; FOI email decoded from Cloudflare cfemail attribute on FOI page. 2026-09-12: both pages are 403 to local fetch (documented WAF); reached via server-side WebFetch instead. Press decoded to gstt.press@nhs.net, matching the primary. The FOI token as relayed decoded one character off (w-stt.foi@nhs.net), consistent with a transcription artefact rather than a changed address, so gstt.foi@nhs.net left as primary.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Both press and FOI emails on hdft.nhs.uk are obfuscated as [email protected]; confirmed contact phone numbers (press 01423 557470) but emails not extractable</t>
+          <t>Both press and FOI emails on hdft.nhs.uk are obfuscated as [email protected]; confirmed contact phone numbers (press 01423 557470) but emails not extractable 2026-09-12: the [email protected] obfuscation on hdft.nhs.uk was decoded this run (Cloudflare cfemail) - the contact page carries hdft.hello@nhs.net and hdft.foi@nhs.net, i.e. the values already held in the _alt fields; the earlier 'emails not extractable' note is superseded. Neither primary (communications@hdft.nhs.uk, foi@hdft.nhs.uk) appears on the page.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/news/media-enquiries-and-contacts/</t>
+          <t>https://www.mtw.nhs.uk/media-enquiries-and-press/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-04: source URLs refreshed (old /contact/ now 404); FOI mtw-tr.foiadmin@nhs.net confirmed live, press email unchanged (media page blocks automated fetch).</t>
+          <t>2026-07-04: source URLs refreshed (old /contact/ now 404); FOI mtw-tr.foiadmin@nhs.net confirmed live, press email unchanged (media page blocks automated fetch). press_source_url updated 2026-09-12: previous /news/media-enquiries-and-contacts/ now 404s; live media page is /media-enquiries-and-press/ and it carries the same mtw-tr.communications@nhs.net (address unchanged).</t>
         </is>
       </c>
     </row>
@@ -4463,10 +4463,14 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.nnuh.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>https://www.nnuh.nhs.uk/departments/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>foi_source_url updated 2026-09-12: old /about-us/freedom-of-information/ now 301-redirects to /departments/freedom-of-information/; foi@nnuh.nhs.uk unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4745,7 +4749,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cloudflare email-protection decoded for FOI</t>
+          <t>Cloudflare email-protection decoded for FOI 2026-09-12: contact page decoded (cfemail) - the press section reads 'Press office - For media enquiries contact press.office@nwas.nhs.uk', i.e. the _alt value; the primary press@nwas.nhs.uk does not appear on the page. Left unchanged per the alt-match rule, but worth a human check on which inbox NWAS now prefers.</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6852,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026. 2026-07-04: FOI source URL refreshed (old /about-us/ page 404); still online-form only (thh.disclosure-log.co.uk), no email published.</t>
+          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026. 2026-07-04: FOI source URL refreshed (old /about-us/ page 404); still online-form only (thh.disclosure-log.co.uk), no email published. 2026-09-12: FOI page carries no email address at all - the trust directs all requests to its online request form (consistent with the thh@infreemation.co.uk portal already held as primary) or to post. No change made.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -3860,10 +3860,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>FOIRequests@lhch.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>FOI@lwh.nhs.uk</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>https://www.uhliverpool.nhs.uk/freedom-information-requests-lwh</t>
@@ -3871,7 +3875,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme | foi_source_url updated 2026-07-18 to live UHL group FOI page (FOI@lwh.nhs.uk confirmed); prior liverpoolwomens.nhs.uk PDF now redirects to the group site. Group submission inbox FOIRequests@liverpoolft.nhs.uk also seen (not adopted as primary)</t>
+          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme | foi_source_url updated 2026-07-18 to live UHL group FOI page (FOI@lwh.nhs.uk confirmed); prior liverpoolwomens.nhs.uk PDF now redirects to the group site. Group submission inbox FOIRequests@liverpoolft.nhs.uk also seen (not adopted as primary) FOI primary updated 2026-09-26 from https://www.uhliverpool.nhs.uk/freedom-information-requests-lwh; prior value moved to _alt. The LWH freedom-of-information page on the NHS University Hospitals of Liverpool Group site now directs requesters to FOIRequests@lhch.nhs.uk and to Information Governance, Health Records, Liverpool Heart and Chest Hospital - i.e. FOI is handled by the group Access to Information team (tel 0151 702 1336 / 4645), not a LWH-specific inbox.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -1682,7 +1682,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/contact/press/</t>
+          <t>https://www.cntw.nhs.uk/about-us/contact-us/media</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1693,12 +1693,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/foi/request/</t>
+          <t>https://www.cntw.nhs.uk/about-us/trust/other-corporate-information/information-held-trust/freedom-information</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cloudflare email-protection decoded</t>
+          <t>Cloudflare email-protection decoded 2026-10-03: source URLs updated (old /contact/press/ 404s; /foi/request/ redirects); both addresses re-confirmed unchanged.</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.ekhuft.nhs.uk/patients-and-visitors/about-us/freedom-of-information/</t>
+          <t>https://www.ekhuft.nhs.uk/about-us/foi/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration. FOI source URL resolved 2026-07-30 to /patients-and-visitors/about-us/freedom-of-information/ (site migration complete); ekh-tr.FOI@nhs.net confirmed on page, address unchanged.</t>
+          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration. FOI source URL resolved 2026-07-30 to /patients-and-visitors/about-us/freedom-of-information/ (site migration complete); ekh-tr.FOI@nhs.net confirmed on page, address unchanged. 2026-10-03: foi_source_url updated (old page redirects to /about-us/foi/); address re-confirmed unchanged.</t>
         </is>
       </c>
     </row>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.qehkl.nhs.uk/freedom-of-information.asp</t>
+          <t>https://www.qehkl.nhs.uk/about-us/information-requests/</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FOI uses combined data protection / FOI inbox press source URL updated 2026-07-30: /news-and-events/media-enquiries/ now 404s, page moved to /about-us/media-enquiries/; media.enquiries@qehkl.nhs.uk confirmed there, address unchanged. Note the FOI page designates foi@qehkl.nhs.uk (currently held in _alt) while dpa@ is the data-protection inbox.</t>
+          <t>FOI uses combined data protection / FOI inbox press source URL updated 2026-07-30: /news-and-events/media-enquiries/ now 404s, page moved to /about-us/media-enquiries/; media.enquiries@qehkl.nhs.uk confirmed there, address unchanged. Note the FOI page designates foi@qehkl.nhs.uk (currently held in _alt) while dpa@ is the data-protection inbox. 2026-10-03: foi_source_url updated (freedom-of-information.asp redirects to /about-us/information-requests/); that page names foi@qehkl.nhs.uk (current _alt) as THE FOI address and dpa@ as health-records only - primary/alt swap left for manual review.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -1407,13 +1407,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>cwp.essential@nhs.net</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>jodie.denrico@cwp.nhs.uk</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.cwp.nhs.uk/contact/media-enquiries</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1424,12 +1428,12 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.cwp.nhs.uk/contact/freedom-information</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cheshire and Wirral Partnership website Cloudflare bot-protected; could not retrieve contact pages; Cheshire &amp; Wirral Partnership: all contact and FOI pages returned 403 to WebFetch (server-side bot block).</t>
+          <t>Cheshire and Wirral Partnership website Cloudflare bot-protected; could not retrieve contact pages; Cheshire &amp; Wirral Partnership: all contact and FOI pages returned 403 to WebFetch (server-side bot block). | press primary updated 2026-10-10 from https://www.cwp.nhs.uk/contact/media-enquiries (read via local headless Playwright; curl and WebFetch get Cloudflare 403); prior value jodie.denrico@cwp.nhs.uk moved to _alt. FOI cwp.foi@nhs.net confirmed 2026-10-10 on /contact/freedom-information, source URL updated.</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4670,12 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.combined.nhs.uk/about/policies-and-procedures/freedom-of-information/about-freedom-of-information/</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FOI page returned 404 from tested paths and connection reset on combined.nhs.uk; FOI inbox not retrievable; North Staffordshire Combined FOI sub-pages 404; no FOI email published on contact page.</t>
+          <t>FOI page returned 404 from tested paths and connection reset on combined.nhs.uk; FOI inbox not retrievable; North Staffordshire Combined FOI sub-pages 404; no FOI email published on contact page. | 2026-10-10: FOIRequests@combined.nhs.uk confirmed on https://www.combined.nhs.uk/about/policies-and-procedures/freedom-of-information/about-freedom-of-information/ (source URL updated from the May 2026 spreadsheet); press address confirmed on contact page.</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5898,11 @@
           <t>https://www.sfh-tr.nhs.uk/about-us/regulatory-information/freedom-of-information/</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-10-10: FOI page shows only the Director of Corporate Affairs internal-review address (sally.brookshanahan@nhs.net), no generic FOI inbox; sfh-tr.information.governance@nhs.net retained unverified. Press address confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2538,35 +2538,39 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>ghc.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>ghccomms@ghc.nhs.uk</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2gnft.comms@nhs.net</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.ghc.nhs.uk/contact-us/</t>
+          <t>https://www.ghc.nhs.uk/get-in-touch/</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>ghc.FOI@nhs.net</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>foi@ghc.nhs.uk</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>FreedomofInformation@ghc.nhs.uk</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://www.ghc.nhs.uk/who-we-are/freedom-of-information/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[2026-10-17] press_email primary updated 2026-10-17 from [https://www.ghc.nhs.uk/get-in-touch/]; prior value moved to _alt [2026-10-17] foi_email primary updated 2026-10-17 from [https://www.ghc.nhs.uk/who-we-are/freedom-of-information/]; prior value moved to _alt</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -4426,22 +4426,22 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>eec.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
           <t>eec.accesstoinfo@nhs.net</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>ccs.accesstoinfo@nhs.net</t>
-        </is>
-      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
+          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV); press and FOI primaries updated 2026-08-08 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us — the merged trust now publishes eec.communications@nhs.net (media) and eec.accesstoinfo@nhs.net (FOI); prior values ccs.communications@nhs.net and ccs.accesstoinfo@nhs.net moved to the _alt fields, displacing the legacy Norfolk Community addresses Communications@nchc.nhs.uk and FreedomOfInformationProvider@nchc.nhs.uk, which are recorded here so they are not lost</t>
+          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV); press and FOI primaries updated 2026-08-08 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us — the merged trust now publishes eec.communications@nhs.net (media) and eec.accesstoinfo@nhs.net (FOI); prior values ccs.communications@nhs.net and ccs.accesstoinfo@nhs.net moved to the _alt fields, displacing the legacy Norfolk Community addresses Communications@nchc.nhs.uk and FreedomOfInformationProvider@nchc.nhs.uk, which are recorded here so they are not lost | foi primary updated 2026-10-24 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact/; prior value eec.accesstoinfo@nhs.net moved to _alt (displacing prior _alt ccs.accesstoinfo@nhs.net)</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.surreyandsussex.nhs.uk/find-contact-us/contact-us/media-and-communications</t>
+          <t>https://www.surreyandsussex.nhs.uk/find-contact-us/media-and-communications</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6542,7 +6542,11 @@
           <t>https://www.surreyandsussex.nhs.uk/about-us/corporate-and-regulatory-information/freedom-information/how-make-request</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>press_source_url updated 2026-10-24 from https://www.surreyandsussex.nhs.uk/find-contact-us/contact-us/media-and-communications to https://www.surreyandsussex.nhs.uk/find-contact-us/media-and-communications (old /find-contact-us/contact-us/media-and-communications page now 404; sash.communications@nhs.net confirmed unchanged on the new page)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -3652,7 +3652,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
+          <t>https://www.lewishamandgreenwich.nhs.uk/for-the-media</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3663,10 +3663,14 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>https://www.lewishamandgreenwich.nhs.uk/foi</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-10-31: press_source_url repointed from https://www.lewishamandgreenwich.nhs.uk/contact-us/ to [https://www.lewishamandgreenwich.nhs.uk/for-the-media] (address unchanged; old page no longer lists it); foi_source_url repointed from https://www.lewishamandgreenwich.nhs.uk/contact-us/ to [https://www.lewishamandgreenwich.nhs.uk/foi] (address unchanged; old page no longer lists it).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3831,12 +3835,12 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.uhliverpool.nhs.uk/contact-us/freedom-information-requests</t>
+          <t>https://www.uhliverpool.nhs.uk/freedom-of-information-requests-luhft</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>now part of NHS University Hospitals of Liverpool Group</t>
+          <t>now part of NHS University Hospitals of Liverpool Group. 2026-10-31: foi_source_url repointed from https://www.uhliverpool.nhs.uk/contact-us/freedom-information-requests to [https://www.uhliverpool.nhs.uk/freedom-of-information-requests-luhft] (address unchanged; old page no longer lists it).</t>
         </is>
       </c>
     </row>
